--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="19226"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\myous\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{5741D43C-C516-4EFD-AEF3-58789B3B00F2}" xr6:coauthVersionLast="32" xr6:coauthVersionMax="32" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8496" xr2:uid="{45A2D40E-73CB-4B64-8B2D-94AEE28124F0}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8496"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,9 +26,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
-    <t>Show Informaiton on Air Waybill</t>
-  </si>
-  <si>
     <t>Consignee Name</t>
   </si>
   <si>
@@ -54,12 +50,6 @@
     <t>Item Quantity</t>
   </si>
   <si>
-    <t>Insurance</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
     <t>Amount</t>
   </si>
   <si>
@@ -81,12 +71,6 @@
     <t>Consignee City ID</t>
   </si>
   <si>
-    <t>Product Type ID</t>
-  </si>
-  <si>
-    <t>Replacement Product Type ID</t>
-  </si>
-  <si>
     <t>Estimated Weight (kg)</t>
   </si>
   <si>
@@ -100,12 +84,27 @@
   </si>
   <si>
     <t>Pickup Date (YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>Item Product Type ID</t>
+  </si>
+  <si>
+    <t>Replacement Item Product Type ID</t>
+  </si>
+  <si>
+    <t>Item Price</t>
+  </si>
+  <si>
+    <t>Item Insurance</t>
+  </si>
+  <si>
+    <t>Show Information on Air Waybill</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -450,7 +449,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C05B604C-4CD9-4490-B216-9108DF735C28}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -463,11 +462,12 @@
     <col min="7" max="8" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="29.77734375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="26" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="23.5546875" bestFit="1" customWidth="1"/>
@@ -481,79 +481,79 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R1" t="s">
+        <v>11</v>
+      </c>
+      <c r="S1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" t="s">
+      <c r="V1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="W1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="X1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y1" t="s">
         <v>18</v>
-      </c>
-      <c r="L1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" t="s">
-        <v>24</v>
-      </c>
-      <c r="T1" t="s">
-        <v>12</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -134,8 +134,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,106 +454,106 @@
   <dimension ref="A1:Y1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>18</v>
       </c>
     </row>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -32,12 +32,6 @@
     <t>Consignee Address</t>
   </si>
   <si>
-    <t>Consignee Phone Number 2</t>
-  </si>
-  <si>
-    <t>Consignee Phone Number 1</t>
-  </si>
-  <si>
     <t>Consignee Email Address</t>
   </si>
   <si>
@@ -99,6 +93,12 @@
   </si>
   <si>
     <t>Show Information on Air Waybill</t>
+  </si>
+  <si>
+    <t>Consignee Phone Number 1 (0300-0000000)</t>
+  </si>
+  <si>
+    <t>Consignee Phone Number 2 (0300-0000000)</t>
   </si>
 </sst>
 </file>
@@ -460,14 +460,14 @@
     <col min="4" max="4" width="15.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="37.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.21875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="26" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -482,16 +482,16 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -500,61 +500,61 @@
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="V1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -44,9 +44,6 @@
     <t>Item Quantity</t>
   </si>
   <si>
-    <t>Amount</t>
-  </si>
-  <si>
     <t>Special Instructions</t>
   </si>
   <si>
@@ -86,19 +83,22 @@
     <t>Replacement Item Product Type ID</t>
   </si>
   <si>
-    <t>Item Price</t>
-  </si>
-  <si>
     <t>Item Insurance</t>
   </si>
   <si>
     <t>Show Information on Air Waybill</t>
   </si>
   <si>
-    <t>Consignee Phone Number 1 (0300-0000000)</t>
-  </si>
-  <si>
-    <t>Consignee Phone Number 2 (0300-0000000)</t>
+    <t>Product Value</t>
+  </si>
+  <si>
+    <t>Collection Amount</t>
+  </si>
+  <si>
+    <t>Consignee Phone Number 2 (03000000000)</t>
+  </si>
+  <si>
+    <t>Consignee Phone Number 1 (03000000000)</t>
   </si>
 </sst>
 </file>
@@ -460,14 +460,14 @@
     <col min="4" max="4" width="15.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="37.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.21875" style="1" customWidth="1"/>
     <col min="14" max="14" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="26" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -476,22 +476,22 @@
     <col min="21" max="21" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="18" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -500,10 +500,10 @@
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>2</v>
@@ -512,7 +512,7 @@
         <v>3</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>4</v>
@@ -521,40 +521,40 @@
         <v>5</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="P1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="S1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -59,9 +59,6 @@
     <t>Pickup Address ID</t>
   </si>
   <si>
-    <t>Consignee City ID</t>
-  </si>
-  <si>
     <t>Estimated Weight (kg)</t>
   </si>
   <si>
@@ -99,6 +96,9 @@
   </si>
   <si>
     <t>Consignee Phone Number 1 (03000000000)</t>
+  </si>
+  <si>
+    <t>Consignee City Name</t>
   </si>
 </sst>
 </file>
@@ -457,7 +457,7 @@
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -488,10 +488,10 @@
         <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -500,10 +500,10 @@
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>2</v>
@@ -512,7 +512,7 @@
         <v>3</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>4</v>
@@ -521,13 +521,13 @@
         <v>5</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>7</v>
@@ -536,25 +536,25 @@
         <v>8</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>Consignee City Name</t>
+  </si>
+  <si>
+    <t>Charges Mode ID</t>
   </si>
 </sst>
 </file>
@@ -451,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -478,9 +481,10 @@
     <col min="23" max="23" width="17.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -555,6 +559,9 @@
       </c>
       <c r="Y1" s="1" t="s">
         <v>14</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\sonic\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -102,12 +102,72 @@
   </si>
   <si>
     <t>Charges Mode ID</t>
+  </si>
+  <si>
+    <t>Item Product Type ID 2</t>
+  </si>
+  <si>
+    <t>Item Description 2</t>
+  </si>
+  <si>
+    <t>Item Quantity 2</t>
+  </si>
+  <si>
+    <t>Item Insurance 2</t>
+  </si>
+  <si>
+    <t>Product Value 2</t>
+  </si>
+  <si>
+    <t>Item Product Type ID 3</t>
+  </si>
+  <si>
+    <t>Item Description 3</t>
+  </si>
+  <si>
+    <t>Item Quantity 3</t>
+  </si>
+  <si>
+    <t>Item Insurance 4</t>
+  </si>
+  <si>
+    <t>Product Value 3</t>
+  </si>
+  <si>
+    <t>Item Product Type ID 4</t>
+  </si>
+  <si>
+    <t>Item Description 4</t>
+  </si>
+  <si>
+    <t>Item Quantity 4</t>
+  </si>
+  <si>
+    <t>Product Value 4</t>
+  </si>
+  <si>
+    <t>Item Product Type ID 5</t>
+  </si>
+  <si>
+    <t>Item Description 5</t>
+  </si>
+  <si>
+    <t>Item Quantity 5</t>
+  </si>
+  <si>
+    <t>Item Insurance 5</t>
+  </si>
+  <si>
+    <t>Product Value 5</t>
+  </si>
+  <si>
+    <t>Item Insurance 3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -454,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:AT1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -471,20 +531,21 @@
     <col min="13" max="13" width="12.21875" style="1" customWidth="1"/>
     <col min="14" max="14" width="13.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="35" width="12.33203125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="23.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="15" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -531,40 +592,101 @@
         <v>20</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -162,6 +162,9 @@
   </si>
   <si>
     <t>Item Insurance 3</t>
+  </si>
+  <si>
+    <t>Try and Buy Charges</t>
   </si>
 </sst>
 </file>
@@ -514,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AT1"/>
+  <dimension ref="A1:AU1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -545,7 +548,7 @@
     <col min="46" max="46" width="15" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -683,6 +686,9 @@
       </c>
       <c r="AT1" s="1" t="s">
         <v>25</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a1a46e8625ea525f/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8496"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -104,73 +104,88 @@
     <t>Charges Mode ID</t>
   </si>
   <si>
-    <t>Item Product Type ID 2</t>
-  </si>
-  <si>
-    <t>Item Description 2</t>
-  </si>
-  <si>
-    <t>Item Quantity 2</t>
-  </si>
-  <si>
-    <t>Item Insurance 2</t>
-  </si>
-  <si>
-    <t>Product Value 2</t>
-  </si>
-  <si>
-    <t>Item Product Type ID 3</t>
-  </si>
-  <si>
-    <t>Item Description 3</t>
-  </si>
-  <si>
-    <t>Item Quantity 3</t>
-  </si>
-  <si>
-    <t>Item Insurance 4</t>
-  </si>
-  <si>
-    <t>Product Value 3</t>
-  </si>
-  <si>
-    <t>Item Product Type ID 4</t>
-  </si>
-  <si>
-    <t>Item Description 4</t>
-  </si>
-  <si>
-    <t>Item Quantity 4</t>
-  </si>
-  <si>
-    <t>Product Value 4</t>
-  </si>
-  <si>
-    <t>Item Product Type ID 5</t>
-  </si>
-  <si>
-    <t>Item Description 5</t>
-  </si>
-  <si>
-    <t>Item Quantity 5</t>
-  </si>
-  <si>
-    <t>Item Insurance 5</t>
-  </si>
-  <si>
-    <t>Product Value 5</t>
-  </si>
-  <si>
-    <t>Item Insurance 3</t>
-  </si>
-  <si>
     <t>Try and Buy Charges</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Product Type ID 1</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Description 1</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Quantity 1</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Insurance 1</t>
+  </si>
+  <si>
+    <t>Try and Buy Product Value 1</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Product Type ID 2</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Description 2</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Quantity 2</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Insurance 2</t>
+  </si>
+  <si>
+    <t>Try and Buy Product Value 2</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Product Type ID 3</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Description 3</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Quantity 3</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Insurance 3</t>
+  </si>
+  <si>
+    <t>Try and Buy Product Value 3</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Product Type ID 4</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Description 4</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Quantity 4</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Insurance 4</t>
+  </si>
+  <si>
+    <t>Try and Buy Product Value 4</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Product Type ID 5</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Description 5</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Quantity 5</t>
+  </si>
+  <si>
+    <t>Try and Buy Item Insurance 5</t>
+  </si>
+  <si>
+    <t>Try and Buy Product Value 5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -517,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AU1"/>
+  <dimension ref="A1:AZ1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -534,21 +549,46 @@
     <col min="13" max="13" width="12.21875" style="1" customWidth="1"/>
     <col min="14" max="14" width="13.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="35" width="12.33203125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="23.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23.88671875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="26.21875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="23.88671875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="24" style="1" customWidth="1"/>
+    <col min="39" max="39" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="23.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="15" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -595,100 +635,115 @@
         <v>20</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a1a46e8625ea525f/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>Mode of Payment ID</t>
-  </si>
-  <si>
-    <t>Pickup Date (YYYY-MM-DD)</t>
   </si>
   <si>
     <t>Item Product Type ID</t>
@@ -185,7 +182,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -532,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AZ1"/>
+  <dimension ref="A1:AY1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -577,18 +574,17 @@
     <col min="41" max="41" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="23.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="15" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -596,10 +592,10 @@
         <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -608,10 +604,10 @@
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>2</v>
@@ -620,7 +616,7 @@
         <v>3</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>4</v>
@@ -629,13 +625,13 @@
         <v>5</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>7</v>
@@ -644,106 +640,103 @@
         <v>8</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AQ1" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="AR1" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22730"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22932728-9451-4260-91D5-0B015A0514B4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
+    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="12696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -177,12 +178,15 @@
   </si>
   <si>
     <t>Try and Buy Product Value 5</t>
+  </si>
+  <si>
+    <t>Piece(s)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -528,8 +532,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AY1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AZ1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -582,9 +586,10 @@
     <col min="49" max="49" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="18" style="1" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="16.109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -737,6 +742,9 @@
       </c>
       <c r="AY1" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22932728-9451-4260-91D5-0B015A0514B4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203C1E25-49AE-4BCF-84CD-CFBA52A5D847}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="12696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -180,7 +180,7 @@
     <t>Try and Buy Product Value 5</t>
   </si>
   <si>
-    <t>Piece(s)</t>
+    <t>Pieces Quantity</t>
   </si>
 </sst>
 </file>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203C1E25-49AE-4BCF-84CD-CFBA52A5D847}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7878AFEA-E5E5-4082-BCB6-386213C8135C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="12696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -180,7 +180,7 @@
     <t>Try and Buy Product Value 5</t>
   </si>
   <si>
-    <t>Pieces Quantity</t>
+    <t>Pieces</t>
   </si>
 </sst>
 </file>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23001"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7878AFEA-E5E5-4082-BCB6-386213C8135C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECBBB8D-AC2F-4DE2-B7F5-B3E6C603F23F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="12696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -181,6 +181,9 @@
   </si>
   <si>
     <t>Pieces</t>
+  </si>
+  <si>
+    <t>Self Collection</t>
   </si>
 </sst>
 </file>
@@ -533,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ1"/>
+  <dimension ref="A1:BA1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -544,52 +547,53 @@
     <col min="6" max="6" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="23.88671875" style="1" customWidth="1"/>
-    <col min="22" max="22" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="26.21875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="23.88671875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="24" style="1" customWidth="1"/>
-    <col min="39" max="39" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="16.109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="21.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.21875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.88671875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="26.21875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="23.88671875" style="1" customWidth="1"/>
+    <col min="38" max="38" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="24" style="1" customWidth="1"/>
+    <col min="40" max="40" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="16.109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -618,132 +622,135 @@
         <v>2</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>51</v>
       </c>
     </row>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23001"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECBBB8D-AC2F-4DE2-B7F5-B3E6C603F23F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF73649-B95F-43B9-8893-62746F499D2D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="204" yWindow="2376" windowWidth="17280" windowHeight="8976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>Self Collection</t>
+  </si>
+  <si>
+    <t>Order Date (YYYY-MM-DD)</t>
   </si>
 </sst>
 </file>
@@ -536,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BA1"/>
+  <dimension ref="A1:BB1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -549,51 +552,52 @@
     <col min="9" max="9" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.33203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.21875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.88671875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="26.21875" style="1" customWidth="1"/>
-    <col min="27" max="27" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="23.88671875" style="1" customWidth="1"/>
-    <col min="38" max="38" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="24" style="1" customWidth="1"/>
-    <col min="40" max="40" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="16.109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.21875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="23.88671875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="26.21875" style="1" customWidth="1"/>
+    <col min="28" max="28" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="23.88671875" style="1" customWidth="1"/>
+    <col min="39" max="39" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="24" style="1" customWidth="1"/>
+    <col min="41" max="41" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="16.109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -628,129 +632,132 @@
         <v>3</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>51</v>
       </c>
     </row>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF73649-B95F-43B9-8893-62746F499D2D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D191EDBD-724C-4DDE-B98E-413812817ED0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="204" yWindow="2376" windowWidth="17280" windowHeight="8976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -187,6 +187,21 @@
   </si>
   <si>
     <t>Order Date (YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 1</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 2</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 3</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 4</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 5</t>
   </si>
 </sst>
 </file>
@@ -539,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BB1"/>
+  <dimension ref="A1:BG1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -595,9 +610,10 @@
     <col min="52" max="52" width="18" style="1" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="54" max="54" width="16.109375" style="1" customWidth="1"/>
+    <col min="55" max="59" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -759,6 +775,21 @@
       </c>
       <c r="BB1" s="1" t="s">
         <v>51</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D191EDBD-724C-4DDE-B98E-413812817ED0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F45DFE-2637-4F9A-9445-C423D3F3884A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -202,6 +202,9 @@
   </si>
   <si>
     <t>Shipper Reference Number 5</t>
+  </si>
+  <si>
+    <t>Open Shipment</t>
   </si>
 </sst>
 </file>
@@ -554,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BG1"/>
+  <dimension ref="A1:BH1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -613,7 +616,7 @@
     <col min="55" max="59" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -790,6 +793,9 @@
       </c>
       <c r="BG1" t="s">
         <v>58</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F45DFE-2637-4F9A-9445-C423D3F3884A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8D691F4-0960-4BF3-B113-A1ADA8FB09AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -205,6 +205,9 @@
   </si>
   <si>
     <t>Open Shipment</t>
+  </si>
+  <si>
+    <t>Return Address ID</t>
   </si>
 </sst>
 </file>
@@ -557,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BI1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -616,7 +619,7 @@
     <col min="55" max="59" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -796,6 +799,9 @@
       </c>
       <c r="BH1" t="s">
         <v>59</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8D691F4-0960-4BF3-B113-A1ADA8FB09AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CC5588-B772-40FB-9A61-6D1F9CB0BB78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -205,9 +205,6 @@
   </si>
   <si>
     <t>Open Shipment</t>
-  </si>
-  <si>
-    <t>Return Address ID</t>
   </si>
 </sst>
 </file>
@@ -560,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI1"/>
+  <dimension ref="A1:BH1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -619,7 +616,7 @@
     <col min="55" max="59" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -799,9 +796,6 @@
       </c>
       <c r="BH1" t="s">
         <v>59</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CC5588-B772-40FB-9A61-6D1F9CB0BB78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F45DFE-2637-4F9A-9445-C423D3F3884A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F45DFE-2637-4F9A-9445-C423D3F3884A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA5FC74-B01B-4822-80E2-54D55270DED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -205,6 +205,12 @@
   </si>
   <si>
     <t>Open Shipment</t>
+  </si>
+  <si>
+    <t>Trax Center/Franchise Type</t>
+  </si>
+  <si>
+    <t>Trax Center/Franchise ID</t>
   </si>
 </sst>
 </file>
@@ -557,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BJ1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -614,9 +620,12 @@
     <col min="53" max="53" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="54" max="54" width="16.109375" style="1" customWidth="1"/>
     <col min="55" max="59" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="21.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -796,6 +805,12 @@
       </c>
       <c r="BH1" t="s">
         <v>59</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA5FC74-B01B-4822-80E2-54D55270DED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94E993D-2DB7-4FA4-8422-E5F3B8C73D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2088" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -205,12 +205,6 @@
   </si>
   <si>
     <t>Open Shipment</t>
-  </si>
-  <si>
-    <t>Trax Center/Franchise Type</t>
-  </si>
-  <si>
-    <t>Trax Center/Franchise ID</t>
   </si>
 </sst>
 </file>
@@ -563,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BJ1"/>
+  <dimension ref="A1:BH1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -625,7 +619,7 @@
     <col min="62" max="62" width="21.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -805,12 +799,6 @@
       </c>
       <c r="BH1" t="s">
         <v>59</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>60</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94E993D-2DB7-4FA4-8422-E5F3B8C73D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F45DFE-2637-4F9A-9445-C423D3F3884A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2088" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -614,9 +614,6 @@
     <col min="53" max="53" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="54" max="54" width="16.109375" style="1" customWidth="1"/>
     <col min="55" max="59" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="21.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:60" x14ac:dyDescent="0.3">

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F45DFE-2637-4F9A-9445-C423D3F3884A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE99EAE-2746-43AD-B4E5-63D48A4D5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -205,6 +205,9 @@
   </si>
   <si>
     <t>Open Shipment</t>
+  </si>
+  <si>
+    <t>Parcel Value</t>
   </si>
 </sst>
 </file>
@@ -557,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BI1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -616,7 +619,7 @@
     <col min="55" max="59" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -796,6 +799,9 @@
       </c>
       <c r="BH1" t="s">
         <v>59</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE99EAE-2746-43AD-B4E5-63D48A4D5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D95CBE-1C12-47AB-BFB4-CFCA0B1FCB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -617,6 +617,7 @@
     <col min="53" max="53" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="54" max="54" width="16.109375" style="1" customWidth="1"/>
     <col min="55" max="59" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:61" x14ac:dyDescent="0.3">
@@ -800,7 +801,7 @@
       <c r="BH1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>60</v>
       </c>
     </row>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D95CBE-1C12-47AB-BFB4-CFCA0B1FCB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -208,12 +207,18 @@
   </si>
   <si>
     <t>Parcel Value</t>
+  </si>
+  <si>
+    <t>Consignee Address Latitude</t>
+  </si>
+  <si>
+    <t>Consignee Address Longitude</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -559,8 +564,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:BK1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -571,56 +576,56 @@
     <col min="6" max="6" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.21875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="23.88671875" style="1" customWidth="1"/>
-    <col min="24" max="24" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="26.21875" style="1" customWidth="1"/>
-    <col min="28" max="28" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="23.88671875" style="1" customWidth="1"/>
-    <col min="39" max="39" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="24" style="1" customWidth="1"/>
-    <col min="41" max="41" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="16.109375" style="1" customWidth="1"/>
-    <col min="55" max="59" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="8.88671875" style="1"/>
+    <col min="10" max="12" width="21.33203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.21875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="23.88671875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="26.21875" style="1" customWidth="1"/>
+    <col min="30" max="30" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="23.88671875" style="1" customWidth="1"/>
+    <col min="41" max="41" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="24" style="1" customWidth="1"/>
+    <col min="43" max="43" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="16.109375" style="1" customWidth="1"/>
+    <col min="57" max="61" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -649,159 +654,165 @@
         <v>2</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>60</v>
       </c>
     </row>

--- a/public/file/Trax Book Shipment Template.xlsx
+++ b/public/file/Trax Book Shipment Template.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -213,6 +213,12 @@
   </si>
   <si>
     <t>Consignee Address Longitude</t>
+  </si>
+  <si>
+    <t>Retail Pickup Store ID</t>
+  </si>
+  <si>
+    <t>Retail Deliver Store ID</t>
   </si>
 </sst>
 </file>
@@ -565,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BK1"/>
+  <dimension ref="A1:BM1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -625,7 +631,7 @@
     <col min="63" max="63" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -814,6 +820,12 @@
       </c>
       <c r="BK1" s="1" t="s">
         <v>60</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
